--- a/eflow-diga/build/2.0.0-draft/all-profiles.xlsx
+++ b/eflow-diga/build/2.0.0-draft/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7398" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7398" uniqueCount="785">
   <si>
     <t>Property</t>
   </si>
@@ -1423,9 +1423,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/rx-prescription-process-identifier-extension}
 </t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
@@ -3561,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="110">
@@ -3569,7 +3566,7 @@
         <v>4</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="111">
@@ -3585,7 +3582,7 @@
         <v>8</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="113">
@@ -3593,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="114">
@@ -3647,7 +3644,7 @@
         <v>23</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="121">
@@ -3683,7 +3680,7 @@
         <v>31</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="126">
@@ -3691,7 +3688,7 @@
         <v>33</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="127">
@@ -14243,10 +14240,10 @@
         <v>451</v>
       </c>
       <c r="M101" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>126</v>
@@ -14319,13 +14316,13 @@
         <v>392</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C102" t="s" s="2">
         <v>448</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E102" t="s" s="2">
         <v>123</v>
@@ -14347,13 +14344,13 @@
         <v>77</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>126</v>
@@ -14426,13 +14423,13 @@
         <v>392</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>448</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E103" t="s" s="2">
         <v>123</v>
@@ -14454,13 +14451,13 @@
         <v>77</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>126</v>
@@ -14533,13 +14530,13 @@
         <v>392</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>448</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E104" t="s" s="2">
         <v>77</v>
@@ -14561,7 +14558,7 @@
         <v>77</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>32</v>
@@ -14638,13 +14635,13 @@
         <v>392</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>448</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E105" t="s" s="2">
         <v>77</v>
@@ -14666,7 +14663,7 @@
         <v>77</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>81</v>
@@ -14743,10 +14740,10 @@
         <v>392</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14850,10 +14847,10 @@
         <v>392</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14879,13 +14876,13 @@
         <v>135</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="N107" t="s" s="2">
+      <c r="O107" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P107" s="2"/>
       <c r="Q107" t="s" s="2">
@@ -14923,7 +14920,7 @@
         <v>77</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AD107" s="2"/>
       <c r="AE107" t="s" s="2">
@@ -14933,7 +14930,7 @@
         <v>95</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>78</v>
@@ -14953,13 +14950,13 @@
         <v>392</v>
       </c>
       <c r="B108" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="D108" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="D108" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="E108" t="s" s="2">
         <v>77</v>
@@ -14981,16 +14978,16 @@
         <v>77</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="N108" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="O108" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
@@ -15001,7 +14998,7 @@
         <v>77</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>77</v>
@@ -15040,7 +15037,7 @@
         <v>77</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -15060,13 +15057,13 @@
         <v>392</v>
       </c>
       <c r="B109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="D109" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="D109" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="E109" t="s" s="2">
         <v>77</v>
@@ -15088,16 +15085,16 @@
         <v>77</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="N109" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O109" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -15108,7 +15105,7 @@
         <v>77</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>77</v>
@@ -15147,7 +15144,7 @@
         <v>77</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>78</v>
@@ -15167,10 +15164,10 @@
         <v>392</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -15193,13 +15190,13 @@
         <v>77</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>274</v>
@@ -15252,7 +15249,7 @@
         <v>77</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>78</v>
@@ -15272,10 +15269,10 @@
         <v>392</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -15301,13 +15298,13 @@
         <v>130</v>
       </c>
       <c r="M111" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="P111" s="2"/>
       <c r="Q111" t="s" s="2">
@@ -15315,7 +15312,7 @@
       </c>
       <c r="R111" s="2"/>
       <c r="S111" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>77</v>
@@ -15336,11 +15333,11 @@
         <v>284</v>
       </c>
       <c r="Z111" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AA111" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AA111" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="AB111" t="s" s="2">
         <v>77</v>
       </c>
@@ -15357,7 +15354,7 @@
         <v>77</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>86</v>
@@ -15377,10 +15374,10 @@
         <v>392</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15403,13 +15400,13 @@
         <v>77</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
@@ -15439,11 +15436,11 @@
         <v>293</v>
       </c>
       <c r="Z112" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AA112" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AA112" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AB112" t="s" s="2">
         <v>77</v>
       </c>
@@ -15460,7 +15457,7 @@
         <v>77</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>78</v>
@@ -15480,10 +15477,10 @@
         <v>392</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15509,13 +15506,13 @@
         <v>289</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N113" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="N113" t="s" s="2">
+      <c r="O113" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="P113" s="2"/>
       <c r="Q113" t="s" s="2">
@@ -15544,11 +15541,11 @@
         <v>284</v>
       </c>
       <c r="Z113" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AA113" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="AA113" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="AB113" t="s" s="2">
         <v>77</v>
       </c>
@@ -15565,7 +15562,7 @@
         <v>77</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>78</v>
@@ -15585,10 +15582,10 @@
         <v>392</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -15611,16 +15608,16 @@
         <v>149</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P114" s="2"/>
       <c r="Q114" t="s" s="2">
@@ -15670,7 +15667,7 @@
         <v>77</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>86</v>
@@ -15690,10 +15687,10 @@
         <v>392</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -15793,10 +15790,10 @@
         <v>392</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -15898,13 +15895,13 @@
         <v>392</v>
       </c>
       <c r="B117" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="D117" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="D117" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="E117" t="s" s="2">
         <v>77</v>
@@ -15926,13 +15923,13 @@
         <v>77</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -16003,10 +16000,10 @@
         <v>392</v>
       </c>
       <c r="B118" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -16106,10 +16103,10 @@
         <v>392</v>
       </c>
       <c r="B119" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16211,10 +16208,10 @@
         <v>392</v>
       </c>
       <c r="B120" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C120" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16254,7 +16251,7 @@
       </c>
       <c r="R120" s="2"/>
       <c r="S120" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="T120" t="s" s="2">
         <v>77</v>
@@ -16316,10 +16313,10 @@
         <v>392</v>
       </c>
       <c r="B121" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -16360,7 +16357,7 @@
         <v>77</v>
       </c>
       <c r="T121" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U121" t="s" s="2">
         <v>77</v>
@@ -16379,7 +16376,7 @@
       </c>
       <c r="Z121" s="2"/>
       <c r="AA121" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AB121" t="s" s="2">
         <v>77</v>
@@ -16417,10 +16414,10 @@
         <v>392</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -16522,10 +16519,10 @@
         <v>392</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -16627,10 +16624,10 @@
         <v>392</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -16656,7 +16653,7 @@
         <v>135</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>261</v>
@@ -16732,10 +16729,10 @@
         <v>392</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -16835,10 +16832,10 @@
         <v>392</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -16940,10 +16937,10 @@
         <v>392</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -16969,16 +16966,16 @@
         <v>130</v>
       </c>
       <c r="M127" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="O127" t="s" s="2">
+      <c r="P127" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="Q127" t="s" s="2">
         <v>77</v>
@@ -17006,28 +17003,28 @@
         <v>284</v>
       </c>
       <c r="Z127" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AA127" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="AA127" t="s" s="2">
+      <c r="AB127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG127" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>78</v>
@@ -17047,10 +17044,10 @@
         <v>392</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -17076,16 +17073,16 @@
         <v>289</v>
       </c>
       <c r="M128" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N128" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="O128" t="s" s="2">
+      <c r="P128" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="Q128" t="s" s="2">
         <v>77</v>
@@ -17113,28 +17110,28 @@
         <v>255</v>
       </c>
       <c r="Z128" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA128" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AA128" t="s" s="2">
+      <c r="AB128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG128" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>78</v>
@@ -17154,10 +17151,10 @@
         <v>392</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17183,65 +17180,65 @@
         <v>98</v>
       </c>
       <c r="M129" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="O129" t="s" s="2">
+      <c r="P129" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="Q129" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R129" s="2"/>
       <c r="S129" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U129" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="T129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U129" t="s" s="2">
+      <c r="V129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG129" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>78</v>
@@ -17261,10 +17258,10 @@
         <v>392</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17290,13 +17287,13 @@
         <v>87</v>
       </c>
       <c r="M130" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
@@ -17310,43 +17307,43 @@
         <v>77</v>
       </c>
       <c r="U130" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG130" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>78</v>
@@ -17366,10 +17363,10 @@
         <v>392</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -17392,16 +17389,16 @@
         <v>149</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
@@ -17451,7 +17448,7 @@
         <v>77</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>78</v>
@@ -17463,7 +17460,7 @@
         <v>83</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="132">
@@ -17471,10 +17468,10 @@
         <v>392</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -17497,16 +17494,16 @@
         <v>149</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -17556,7 +17553,7 @@
         <v>77</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>78</v>
@@ -17576,10 +17573,10 @@
         <v>392</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -17605,7 +17602,7 @@
         <v>87</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>266</v>
@@ -17681,10 +17678,10 @@
         <v>392</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -17707,16 +17704,16 @@
         <v>149</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="P134" s="2"/>
       <c r="Q134" t="s" s="2">
@@ -17766,7 +17763,7 @@
         <v>77</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>78</v>
@@ -17786,10 +17783,10 @@
         <v>392</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -17889,10 +17886,10 @@
         <v>392</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -17994,10 +17991,10 @@
         <v>392</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18099,10 +18096,10 @@
         <v>392</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18166,7 +18163,7 @@
         <v>256</v>
       </c>
       <c r="AA138" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AB138" t="s" s="2">
         <v>77</v>
@@ -18204,10 +18201,10 @@
         <v>392</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18233,10 +18230,10 @@
         <v>354</v>
       </c>
       <c r="M139" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O139" t="s" s="2">
         <v>262</v>
@@ -18309,10 +18306,10 @@
         <v>392</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -18414,10 +18411,10 @@
         <v>392</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -18440,13 +18437,13 @@
         <v>77</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>274</v>
@@ -18499,7 +18496,7 @@
         <v>77</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>78</v>
@@ -18519,10 +18516,10 @@
         <v>392</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -18545,13 +18542,13 @@
         <v>77</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M142" t="s" s="2">
+      <c r="N142" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>274</v>
@@ -18604,7 +18601,7 @@
         <v>77</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>78</v>
@@ -18624,10 +18621,10 @@
         <v>392</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -18653,10 +18650,10 @@
         <v>143</v>
       </c>
       <c r="M143" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -18707,7 +18704,7 @@
         <v>77</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>78</v>
@@ -18727,10 +18724,10 @@
         <v>392</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -18830,10 +18827,10 @@
         <v>392</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -18935,10 +18932,10 @@
         <v>392</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -19042,10 +19039,10 @@
         <v>392</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19071,16 +19068,16 @@
         <v>289</v>
       </c>
       <c r="M147" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>312</v>
       </c>
       <c r="P147" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>77</v>
@@ -19108,11 +19105,11 @@
         <v>293</v>
       </c>
       <c r="Z147" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AA147" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AA147" t="s" s="2">
-        <v>614</v>
-      </c>
       <c r="AB147" t="s" s="2">
         <v>77</v>
       </c>
@@ -19129,7 +19126,7 @@
         <v>77</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>78</v>
@@ -19149,10 +19146,10 @@
         <v>392</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19175,13 +19172,13 @@
         <v>77</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>274</v>
@@ -19234,7 +19231,7 @@
         <v>77</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>86</v>
@@ -19254,10 +19251,10 @@
         <v>392</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19357,10 +19354,10 @@
         <v>392</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19462,10 +19459,10 @@
         <v>392</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19567,10 +19564,10 @@
         <v>392</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19672,10 +19669,10 @@
         <v>392</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -19777,10 +19774,10 @@
         <v>392</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -19882,10 +19879,10 @@
         <v>392</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -19908,13 +19905,13 @@
         <v>77</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>274</v>
@@ -19967,7 +19964,7 @@
         <v>77</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>78</v>
@@ -19987,10 +19984,10 @@
         <v>392</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -20013,16 +20010,16 @@
         <v>77</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P156" s="2"/>
       <c r="Q156" t="s" s="2">
@@ -20072,7 +20069,7 @@
         <v>77</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>78</v>
@@ -20092,10 +20089,10 @@
         <v>392</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20195,10 +20192,10 @@
         <v>392</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20300,10 +20297,10 @@
         <v>392</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20405,10 +20402,10 @@
         <v>392</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -20472,7 +20469,7 @@
         <v>256</v>
       </c>
       <c r="AA160" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AB160" t="s" s="2">
         <v>77</v>
@@ -20510,10 +20507,10 @@
         <v>392</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -20615,10 +20612,10 @@
         <v>392</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20720,10 +20717,10 @@
         <v>392</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20749,10 +20746,10 @@
         <v>289</v>
       </c>
       <c r="M163" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="O163" t="s" s="2">
         <v>312</v>
@@ -20784,11 +20781,11 @@
         <v>293</v>
       </c>
       <c r="Z163" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AA163" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AA163" t="s" s="2">
-        <v>643</v>
-      </c>
       <c r="AB163" t="s" s="2">
         <v>77</v>
       </c>
@@ -20805,7 +20802,7 @@
         <v>77</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>78</v>
@@ -20825,10 +20822,10 @@
         <v>392</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20851,16 +20848,16 @@
         <v>77</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -20910,7 +20907,7 @@
         <v>77</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>78</v>
@@ -20922,7 +20919,7 @@
         <v>83</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="165">
@@ -20930,10 +20927,10 @@
         <v>392</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20956,16 +20953,16 @@
         <v>77</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="M165" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="N165" t="s" s="2">
-        <v>652</v>
-      </c>
       <c r="O165" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21015,7 +21012,7 @@
         <v>77</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>78</v>
@@ -21027,7 +21024,7 @@
         <v>83</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="166">
@@ -21035,10 +21032,10 @@
         <v>392</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21064,10 +21061,10 @@
         <v>161</v>
       </c>
       <c r="M166" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -21118,7 +21115,7 @@
         <v>77</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>78</v>
@@ -21138,10 +21135,10 @@
         <v>392</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21167,10 +21164,10 @@
         <v>161</v>
       </c>
       <c r="M167" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -21221,7 +21218,7 @@
         <v>77</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>78</v>
@@ -21233,7 +21230,7 @@
         <v>77</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="168">
@@ -21241,10 +21238,10 @@
         <v>392</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21267,13 +21264,13 @@
         <v>77</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O168" t="s" s="2">
         <v>274</v>
@@ -21326,7 +21323,7 @@
         <v>77</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>78</v>
@@ -21346,10 +21343,10 @@
         <v>392</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21372,13 +21369,13 @@
         <v>77</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="O169" t="s" s="2">
         <v>274</v>
@@ -21431,7 +21428,7 @@
         <v>77</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>78</v>
@@ -21451,10 +21448,10 @@
         <v>392</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21480,10 +21477,10 @@
         <v>164</v>
       </c>
       <c r="M170" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="N170" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="O170" t="s" s="2">
         <v>391</v>
@@ -21536,7 +21533,7 @@
         <v>77</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>78</v>
@@ -21556,10 +21553,10 @@
         <v>392</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -21582,16 +21579,16 @@
         <v>77</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="O171" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="P171" s="2"/>
       <c r="Q171" t="s" s="2">
@@ -21641,7 +21638,7 @@
         <v>77</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>78</v>
@@ -21653,7 +21650,7 @@
         <v>83</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="172">
@@ -21661,10 +21658,10 @@
         <v>392</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21690,13 +21687,13 @@
         <v>143</v>
       </c>
       <c r="M172" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="P172" s="2"/>
       <c r="Q172" t="s" s="2">
@@ -21746,7 +21743,7 @@
         <v>77</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>78</v>
@@ -21766,10 +21763,10 @@
         <v>392</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21869,10 +21866,10 @@
         <v>392</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21974,10 +21971,10 @@
         <v>392</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22081,10 +22078,10 @@
         <v>392</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -22107,13 +22104,13 @@
         <v>77</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
@@ -22164,7 +22161,7 @@
         <v>77</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>86</v>
@@ -22184,10 +22181,10 @@
         <v>392</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -22213,10 +22210,10 @@
         <v>289</v>
       </c>
       <c r="M177" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N177" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="O177" t="s" s="2">
         <v>312</v>
@@ -22248,11 +22245,11 @@
         <v>293</v>
       </c>
       <c r="Z177" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AA177" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="AA177" t="s" s="2">
-        <v>690</v>
-      </c>
       <c r="AB177" t="s" s="2">
         <v>77</v>
       </c>
@@ -22269,7 +22266,7 @@
         <v>77</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>78</v>
@@ -22289,10 +22286,10 @@
         <v>392</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -22318,10 +22315,10 @@
         <v>289</v>
       </c>
       <c r="M178" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="O178" t="s" s="2">
         <v>312</v>
@@ -22353,11 +22350,11 @@
         <v>293</v>
       </c>
       <c r="Z178" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AA178" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="AA178" t="s" s="2">
-        <v>695</v>
-      </c>
       <c r="AB178" t="s" s="2">
         <v>77</v>
       </c>
@@ -22374,7 +22371,7 @@
         <v>77</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>78</v>
@@ -22394,10 +22391,10 @@
         <v>392</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -22420,13 +22417,13 @@
         <v>77</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="M179" t="s" s="2">
+      <c r="N179" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="O179" t="s" s="2">
         <v>274</v>
@@ -22479,7 +22476,7 @@
         <v>77</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>78</v>
@@ -22499,14 +22496,14 @@
         <v>392</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F180" s="2"/>
       <c r="G180" t="s" s="2">
@@ -22525,16 +22522,16 @@
         <v>77</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="N180" t="s" s="2">
+      <c r="O180" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="P180" s="2"/>
       <c r="Q180" t="s" s="2">
@@ -22584,7 +22581,7 @@
         <v>77</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>78</v>
@@ -22604,10 +22601,10 @@
         <v>392</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -22630,16 +22627,16 @@
         <v>77</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="N181" t="s" s="2">
+      <c r="O181" t="s" s="2">
         <v>709</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>710</v>
       </c>
       <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
@@ -22689,7 +22686,7 @@
         <v>77</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>78</v>
@@ -22706,13 +22703,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -22738,13 +22735,13 @@
         <v>80</v>
       </c>
       <c r="M182" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="N182" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="N182" t="s" s="2">
+      <c r="O182" t="s" s="2">
         <v>719</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>720</v>
       </c>
       <c r="P182" s="2"/>
       <c r="Q182" t="s" s="2">
@@ -22794,7 +22791,7 @@
         <v>77</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>78</v>
@@ -22811,13 +22808,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -22916,13 +22913,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23019,13 +23016,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -23124,13 +23121,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23229,13 +23226,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23261,10 +23258,10 @@
         <v>143</v>
       </c>
       <c r="M187" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
@@ -23303,17 +23300,17 @@
         <v>77</v>
       </c>
       <c r="AC187" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AD187" s="2"/>
       <c r="AE187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>78</v>
@@ -23325,18 +23322,18 @@
         <v>83</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23433,13 +23430,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -23538,13 +23535,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -23645,13 +23642,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -23677,13 +23674,13 @@
         <v>87</v>
       </c>
       <c r="M191" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N191" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="N191" t="s" s="2">
+      <c r="O191" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P191" s="2"/>
       <c r="Q191" t="s" s="2">
@@ -23733,7 +23730,7 @@
         <v>77</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>86</v>
@@ -23750,13 +23747,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -23779,13 +23776,13 @@
         <v>149</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="N192" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -23836,7 +23833,7 @@
         <v>77</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>78</v>
@@ -23845,7 +23842,7 @@
         <v>86</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>106</v>
@@ -23853,13 +23850,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -23885,13 +23882,13 @@
         <v>212</v>
       </c>
       <c r="M193" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="N193" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="N193" t="s" s="2">
+      <c r="O193" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="P193" s="2"/>
       <c r="Q193" t="s" s="2">
@@ -23941,7 +23938,7 @@
         <v>77</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>78</v>
@@ -23950,7 +23947,7 @@
         <v>86</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>77</v>
@@ -23958,13 +23955,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -23990,13 +23987,13 @@
         <v>77</v>
       </c>
       <c r="M194" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -24046,7 +24043,7 @@
         <v>77</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>78</v>
@@ -24063,16 +24060,16 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B195" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="D195" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="D195" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="E195" t="s" s="2">
         <v>77</v>
@@ -24097,10 +24094,10 @@
         <v>143</v>
       </c>
       <c r="M195" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N195" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" s="2"/>
@@ -24151,7 +24148,7 @@
         <v>77</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>78</v>
@@ -24163,18 +24160,18 @@
         <v>83</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24271,13 +24268,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24376,13 +24373,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -24483,13 +24480,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -24515,13 +24512,13 @@
         <v>87</v>
       </c>
       <c r="M199" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N199" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="N199" t="s" s="2">
+      <c r="O199" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="O199" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P199" s="2"/>
       <c r="Q199" t="s" s="2">
@@ -24532,7 +24529,7 @@
         <v>77</v>
       </c>
       <c r="T199" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="U199" t="s" s="2">
         <v>77</v>
@@ -24571,7 +24568,7 @@
         <v>77</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>86</v>
@@ -24588,13 +24585,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -24617,13 +24614,13 @@
         <v>149</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M200" t="s" s="2">
+      <c r="N200" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" s="2"/>
@@ -24674,7 +24671,7 @@
         <v>77</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>78</v>
@@ -24683,7 +24680,7 @@
         <v>86</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>106</v>
@@ -24691,13 +24688,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -24723,13 +24720,13 @@
         <v>212</v>
       </c>
       <c r="M201" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="N201" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="N201" t="s" s="2">
+      <c r="O201" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="P201" s="2"/>
       <c r="Q201" t="s" s="2">
@@ -24779,7 +24776,7 @@
         <v>77</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>78</v>
@@ -24788,7 +24785,7 @@
         <v>86</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AK201" t="s" s="2">
         <v>77</v>
@@ -24796,13 +24793,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -24828,13 +24825,13 @@
         <v>77</v>
       </c>
       <c r="M202" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N202" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N202" t="s" s="2">
+      <c r="O202" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P202" s="2"/>
       <c r="Q202" t="s" s="2">
@@ -24872,17 +24869,17 @@
         <v>77</v>
       </c>
       <c r="AC202" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AD202" s="2"/>
       <c r="AE202" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>78</v>
@@ -24899,13 +24896,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B203" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="C203" t="s" s="2">
         <v>762</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>763</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25002,13 +24999,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B204" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="C204" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="C204" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25107,13 +25104,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B205" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C205" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="C205" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25214,13 +25211,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B206" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="C206" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="C206" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25246,13 +25243,13 @@
         <v>87</v>
       </c>
       <c r="M206" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N206" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="N206" t="s" s="2">
+      <c r="O206" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
@@ -25302,7 +25299,7 @@
         <v>77</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>86</v>
@@ -25319,13 +25316,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B207" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C207" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25348,13 +25345,13 @@
         <v>149</v>
       </c>
       <c r="L207" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="M207" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M207" t="s" s="2">
+      <c r="N207" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -25405,7 +25402,7 @@
         <v>77</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>78</v>
@@ -25414,7 +25411,7 @@
         <v>86</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>106</v>
@@ -25422,13 +25419,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B208" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="C208" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="C208" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -25454,13 +25451,13 @@
         <v>212</v>
       </c>
       <c r="M208" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="N208" t="s" s="2">
         <v>744</v>
       </c>
-      <c r="N208" t="s" s="2">
+      <c r="O208" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="O208" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" t="s" s="2">
@@ -25510,7 +25507,7 @@
         <v>77</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>78</v>
@@ -25519,7 +25516,7 @@
         <v>86</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>77</v>
@@ -25527,13 +25524,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B209" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C209" t="s" s="2">
         <v>774</v>
-      </c>
-      <c r="C209" t="s" s="2">
-        <v>775</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -25559,13 +25556,13 @@
         <v>77</v>
       </c>
       <c r="M209" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N209" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N209" t="s" s="2">
+      <c r="O209" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P209" s="2"/>
       <c r="Q209" t="s" s="2">
@@ -25615,7 +25612,7 @@
         <v>77</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>78</v>
@@ -25632,16 +25629,16 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B210" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="D210" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="D210" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="E210" t="s" s="2">
         <v>77</v>
@@ -25666,13 +25663,13 @@
         <v>143</v>
       </c>
       <c r="M210" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N210" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N210" t="s" s="2">
+      <c r="O210" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -25722,7 +25719,7 @@
         <v>77</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>78</v>
@@ -25739,13 +25736,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -25842,13 +25839,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -25947,13 +25944,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26054,13 +26051,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26086,13 +26083,13 @@
         <v>87</v>
       </c>
       <c r="M214" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="N214" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="N214" t="s" s="2">
+      <c r="O214" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="P214" s="2"/>
       <c r="Q214" t="s" s="2">
@@ -26103,7 +26100,7 @@
         <v>77</v>
       </c>
       <c r="T214" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="U214" t="s" s="2">
         <v>77</v>
@@ -26142,7 +26139,7 @@
         <v>77</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>86</v>
@@ -26159,13 +26156,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26188,13 +26185,13 @@
         <v>149</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M215" t="s" s="2">
+      <c r="N215" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="O215" s="2"/>
       <c r="P215" s="2"/>
@@ -26245,7 +26242,7 @@
         <v>77</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>78</v>
@@ -26254,7 +26251,7 @@
         <v>86</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>106</v>
@@ -26262,13 +26259,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -26291,7 +26288,7 @@
         <v>77</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M216" t="s" s="2">
         <v>399</v>
@@ -26300,7 +26297,7 @@
         <v>400</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="P216" s="2"/>
       <c r="Q216" t="s" s="2">
@@ -26350,7 +26347,7 @@
         <v>77</v>
       </c>
       <c r="AG216" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH216" t="s" s="2">
         <v>78</v>
@@ -26367,13 +26364,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26399,13 +26396,13 @@
         <v>77</v>
       </c>
       <c r="M217" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="N217" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N217" t="s" s="2">
+      <c r="O217" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O217" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P217" s="2"/>
       <c r="Q217" t="s" s="2">
@@ -26455,7 +26452,7 @@
         <v>77</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>78</v>
